--- a/data/trans_orig/P27_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P27_1-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2007</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2007 (tasa de respuesta: 94,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73058</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111222</t>
+          <t>110605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36822</t>
+          <t>37626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64589</t>
+          <t>65959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119267</t>
+          <t>120352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165578</t>
+          <t>165585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146106</t>
+          <t>146866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>192970</t>
+          <t>194206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73038</t>
+          <t>70841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107729</t>
+          <t>109206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229528</t>
+          <t>231820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288754</t>
+          <t>293326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>326287</t>
+          <t>324297</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>387601</t>
+          <t>388394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>377809</t>
+          <t>376185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>442405</t>
+          <t>441556</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>716189</t>
+          <t>716296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>807475</t>
+          <t>807198</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>324839</t>
+          <t>326489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>382990</t>
+          <t>386361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675242</t>
+          <t>673950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>745000</t>
+          <t>745680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1014892</t>
+          <t>1022725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1110838</t>
+          <t>1111791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124391</t>
+          <t>122313</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170891</t>
+          <t>168846</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68386</t>
+          <t>66639</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102604</t>
+          <t>102837</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>200741</t>
+          <t>201900</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>260437</t>
+          <t>260718</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>345221</t>
+          <t>345849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>413846</t>
+          <t>411740</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>281911</t>
+          <t>279590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>342382</t>
+          <t>341208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>643780</t>
+          <t>646529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>738983</t>
+          <t>741371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>568311</t>
+          <t>572629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650369</t>
+          <t>647715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612565</t>
+          <t>615186</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687304</t>
+          <t>688200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1202344</t>
+          <t>1205158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1314949</t>
+          <t>1318150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>449687</t>
+          <t>446911</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>520405</t>
+          <t>521282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>425919</t>
+          <t>428246</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>495486</t>
+          <t>498766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>894268</t>
+          <t>895159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>992187</t>
+          <t>994825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30138</t>
+          <t>30004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30224</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57048</t>
+          <t>57100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85749</t>
+          <t>86551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122605</t>
+          <t>124216</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53862</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84305</t>
+          <t>83228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>147180</t>
+          <t>148575</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>194892</t>
+          <t>195645</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>221289</t>
+          <t>223641</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>268354</t>
+          <t>271719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234593</t>
+          <t>234103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>274939</t>
+          <t>274722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470859</t>
+          <t>470131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>534929</t>
+          <t>534822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131770</t>
+          <t>130652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174567</t>
+          <t>174868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84986</t>
+          <t>85691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120417</t>
+          <t>121935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227103</t>
+          <t>226298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>280519</t>
+          <t>283837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>230451</t>
+          <t>231422</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>293470</t>
+          <t>296676</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131153</t>
+          <t>131336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182464</t>
+          <t>180018</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>375689</t>
+          <t>377526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>456635</t>
+          <t>455145</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>603150</t>
+          <t>611422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>701917</t>
+          <t>700905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>430971</t>
+          <t>426246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>508770</t>
+          <t>506480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1063415</t>
+          <t>1067679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1185269</t>
+          <t>1183049</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1156062</t>
+          <t>1156166</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1263928</t>
+          <t>1261130</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1263771</t>
+          <t>1259286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1374037</t>
+          <t>1369316</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2449376</t>
+          <t>2455889</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2609189</t>
+          <t>2611657</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>938260</t>
+          <t>935564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1043768</t>
+          <t>1040713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1215043</t>
+          <t>1222396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1328197</t>
+          <t>1334990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2178979</t>
+          <t>2188542</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2336426</t>
+          <t>2337659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2012</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2012 (tasa de respuesta: 96,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>30686</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>24417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>47254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33231</t>
+          <t>34200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22770</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45989</t>
+          <t>44959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42448</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70820</t>
+          <t>71660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55670</t>
+          <t>55283</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88039</t>
+          <t>86763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58362</t>
+          <t>57784</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91754</t>
+          <t>92935</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121092</t>
+          <t>120988</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>169992</t>
+          <t>168604</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>823898</t>
+          <t>824631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>864005</t>
+          <t>863671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1154850</t>
+          <t>1153804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1196827</t>
+          <t>1196779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1989327</t>
+          <t>1990692</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2053578</t>
+          <t>2052759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31386</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56573</t>
+          <t>58860</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23885</t>
+          <t>23969</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>63028</t>
+          <t>61023</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95114</t>
+          <t>97350</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92285</t>
+          <t>92779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134554</t>
+          <t>135734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62918</t>
+          <t>63024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98075</t>
+          <t>97693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166050</t>
+          <t>166915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223914</t>
+          <t>220766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>252194</t>
+          <t>250536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316994</t>
+          <t>317360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>208142</t>
+          <t>205747</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>267817</t>
+          <t>264106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>474544</t>
+          <t>474223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559354</t>
+          <t>559488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1420508</t>
+          <t>1417618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1496415</t>
+          <t>1498061</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1307052</t>
+          <t>1308570</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1377970</t>
+          <t>1375254</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2753158</t>
+          <t>2754865</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2848437</t>
+          <t>2853107</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36023</t>
+          <t>35175</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>26777</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>50800</t>
+          <t>52702</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70023</t>
+          <t>71624</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104072</t>
+          <t>106874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45212</t>
+          <t>44835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75380</t>
+          <t>74875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125009</t>
+          <t>123073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174438</t>
+          <t>167960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>343651</t>
+          <t>344078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>382308</t>
+          <t>380685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326922</t>
+          <t>328850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>364671</t>
+          <t>364516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>684521</t>
+          <t>687336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>736421</t>
+          <t>737546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51908</t>
+          <t>52832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84533</t>
+          <t>84595</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41447</t>
+          <t>42026</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71952</t>
+          <t>71463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99157</t>
+          <t>100282</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145295</t>
+          <t>145630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125768</t>
+          <t>126459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173690</t>
+          <t>174872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113378</t>
+          <t>114742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159460</t>
+          <t>158484</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>248695</t>
+          <t>249724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>316470</t>
+          <t>317670</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>406800</t>
+          <t>402685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>482956</t>
+          <t>482004</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>332552</t>
+          <t>332704</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>405248</t>
+          <t>405912</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>759721</t>
+          <t>748803</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>867978</t>
+          <t>861095</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2618938</t>
+          <t>2619676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2713257</t>
+          <t>2714826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2825519</t>
+          <t>2823568</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2912716</t>
+          <t>2909191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5472376</t>
+          <t>5473769</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5594502</t>
+          <t>5601290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2016</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2016 (tasa de respuesta: 97,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29581</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33629</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>30189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>55136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29949</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53440</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>25430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49555</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61338</t>
+          <t>61189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96093</t>
+          <t>94604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75384</t>
+          <t>75857</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114293</t>
+          <t>112301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59580</t>
+          <t>57884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93572</t>
+          <t>92648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146376</t>
+          <t>144222</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>194675</t>
+          <t>195583</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>555020</t>
+          <t>557159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>600793</t>
+          <t>599938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>798385</t>
+          <t>800749</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>843539</t>
+          <t>843133</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1369947</t>
+          <t>1366274</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1430054</t>
+          <t>1428160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47905</t>
+          <t>48263</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80560</t>
+          <t>82506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38093</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68076</t>
+          <t>67679</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>94119</t>
+          <t>96311</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>137708</t>
+          <t>136850</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137661</t>
+          <t>136914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185037</t>
+          <t>186468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118286</t>
+          <t>117208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163577</t>
+          <t>165766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269130</t>
+          <t>269592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337304</t>
+          <t>337000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383485</t>
+          <t>378675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452224</t>
+          <t>454232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,82 +6557,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>18,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>382586</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>352101</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>415822</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>21,38%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>799962</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>748777</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>850060</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>18,78%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>382586</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>346077</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>414627</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>21,32%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>799962</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>751468</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>852888</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1359567</t>
+          <t>1356613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1441754</t>
+          <t>1443979</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1328879</t>
+          <t>1332665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1407458</t>
+          <t>1409870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2713122</t>
+          <t>2711147</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2828596</t>
+          <t>2828381</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23219</t>
+          <t>21262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35437</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18235</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>37419</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>36595</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>65338</t>
+          <t>65307</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73550</t>
+          <t>72965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107277</t>
+          <t>108212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63841</t>
+          <t>64924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98292</t>
+          <t>98030</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146803</t>
+          <t>145666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>195983</t>
+          <t>194876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399031</t>
+          <t>398378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438904</t>
+          <t>435635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400388</t>
+          <t>399427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>438969</t>
+          <t>437932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>809599</t>
+          <t>811304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>867854</t>
+          <t>864990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,87%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67852</t>
+          <t>66902</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106895</t>
+          <t>104355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66012</t>
+          <t>66315</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103283</t>
+          <t>104053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142580</t>
+          <t>144011</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197148</t>
+          <t>195132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195056</t>
+          <t>195171</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258123</t>
+          <t>256315</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178487</t>
+          <t>177058</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237283</t>
+          <t>231667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>385675</t>
+          <t>388526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>473120</t>
+          <t>468785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>556422</t>
+          <t>557632</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646772</t>
+          <t>647098</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>496444</t>
+          <t>494865</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>582406</t>
+          <t>581893</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1075124</t>
+          <t>1077662</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1198770</t>
+          <t>1204641</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2347040</t>
+          <t>2342015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2447734</t>
+          <t>2446655</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2561662</t>
+          <t>2563357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2661142</t>
+          <t>2663717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4943217</t>
+          <t>4937191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5081970</t>
+          <t>5080031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2023</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los días de diario en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>15147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27933</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>38523</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11336</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>32335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55411</t>
+          <t>57198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44599</t>
+          <t>42755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76011</t>
+          <t>76727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57247</t>
+          <t>58456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83755</t>
+          <t>82331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123965</t>
+          <t>123857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>400177</t>
+          <t>400602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>437137</t>
+          <t>438050</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>666023</t>
+          <t>663949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>691776</t>
+          <t>691804</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1074010</t>
+          <t>1076146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1123056</t>
+          <t>1124852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23739</t>
+          <t>22427</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,82 +8838,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>18929</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10741</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>30767</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>33394</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>21549</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>46869</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>18929</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>10432</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>31592</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>33394</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>22575</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>49366</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80881</t>
+          <t>85389</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155330</t>
+          <t>157387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71806</t>
+          <t>72990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120887</t>
+          <t>121406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174868</t>
+          <t>175515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>262398</t>
+          <t>265091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185449</t>
+          <t>186610</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324454</t>
+          <t>327946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156224</t>
+          <t>164178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263030</t>
+          <t>263710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>402040</t>
+          <t>399596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573345</t>
+          <t>569483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1806310</t>
+          <t>1799988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2012267</t>
+          <t>1997913</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1835870</t>
+          <t>1832404</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1986917</t>
+          <t>1975875</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3662682</t>
+          <t>3667177</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3908681</t>
+          <t>3919479</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>38708</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28240</t>
+          <t>29646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>33022</t>
+          <t>32371</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>59862</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47846</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81616</t>
+          <t>81906</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>50960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77055</t>
+          <t>76476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105465</t>
+          <t>105728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147342</t>
+          <t>146950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>526106</t>
+          <t>528188</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>565919</t>
+          <t>566810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>556095</t>
+          <t>554903</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>587767</t>
+          <t>585163</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,47 +9781,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>84,39%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>88,99%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1119790</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1095376</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1143534</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>86,45%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>84,57%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1119790</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1094181</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1143293</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>86,45%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39436</t>
+          <t>39870</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>45711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46077</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77912</t>
+          <t>77357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132613</t>
+          <t>129946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207930</t>
+          <t>206920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109221</t>
+          <t>109573</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158043</t>
+          <t>158878</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>261213</t>
+          <t>264314</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>353271</t>
+          <t>352995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>302036</t>
+          <t>298904</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>451004</t>
+          <t>447137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>275574</t>
+          <t>270899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>374724</t>
+          <t>371236</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>623220</t>
+          <t>619575</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>799691</t>
+          <t>797306</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -10295,17 +10295,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2841420</t>
+          <t>2841419</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2764793</t>
+          <t>2769408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2978128</t>
+          <t>2976681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3086626</t>
+          <t>3084967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3229540</t>
+          <t>3221088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5883324</t>
+          <t>5887289</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6124664</t>
+          <t>6129354</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P27_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P27_1-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75284</t>
+          <t>75162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110605</t>
+          <t>111483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37626</t>
+          <t>37332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65959</t>
+          <t>65208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120352</t>
+          <t>122040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165585</t>
+          <t>167669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146866</t>
+          <t>147147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194206</t>
+          <t>194314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70841</t>
+          <t>72515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109206</t>
+          <t>110401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231820</t>
+          <t>230358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>293326</t>
+          <t>288886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>324297</t>
+          <t>326452</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>388394</t>
+          <t>385368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>376185</t>
+          <t>377845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>441556</t>
+          <t>444368</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>716296</t>
+          <t>722808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>807198</t>
+          <t>807883</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>326489</t>
+          <t>324742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>386361</t>
+          <t>383174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>673950</t>
+          <t>675178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>745680</t>
+          <t>742863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1022725</t>
+          <t>1012742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1111791</t>
+          <t>1109513</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122313</t>
+          <t>123713</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168846</t>
+          <t>172252</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66639</t>
+          <t>68633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102837</t>
+          <t>102993</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>201900</t>
+          <t>204448</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>260718</t>
+          <t>263384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>345849</t>
+          <t>348629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>411740</t>
+          <t>411722</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>279590</t>
+          <t>281105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>341208</t>
+          <t>343709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>646529</t>
+          <t>647259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>741371</t>
+          <t>737775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>572629</t>
+          <t>571301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647715</t>
+          <t>647187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>615186</t>
+          <t>611752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>688200</t>
+          <t>689122</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1205158</t>
+          <t>1209186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1318150</t>
+          <t>1318460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>446911</t>
+          <t>446445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>521282</t>
+          <t>517965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>428246</t>
+          <t>424759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>498766</t>
+          <t>496767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>895159</t>
+          <t>890090</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>994825</t>
+          <t>991464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>32615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30004</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>29776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57100</t>
+          <t>56924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86551</t>
+          <t>84871</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124216</t>
+          <t>124016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53003</t>
+          <t>52796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83228</t>
+          <t>82821</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148575</t>
+          <t>147291</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>195645</t>
+          <t>195792</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>223641</t>
+          <t>222293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>271719</t>
+          <t>268544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234103</t>
+          <t>232609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>274722</t>
+          <t>274309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>470131</t>
+          <t>468900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>534822</t>
+          <t>534522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130652</t>
+          <t>133134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174868</t>
+          <t>174360</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85691</t>
+          <t>85598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121935</t>
+          <t>121230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226298</t>
+          <t>228225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283837</t>
+          <t>282539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>231422</t>
+          <t>230739</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>296676</t>
+          <t>293929</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>130682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180018</t>
+          <t>179420</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>377526</t>
+          <t>377960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>455145</t>
+          <t>457396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>611422</t>
+          <t>607745</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>700905</t>
+          <t>696179</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>426246</t>
+          <t>429423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>506480</t>
+          <t>507219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1067679</t>
+          <t>1056532</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1183049</t>
+          <t>1180308</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1156166</t>
+          <t>1160390</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1261130</t>
+          <t>1266234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1259286</t>
+          <t>1261735</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1369316</t>
+          <t>1367614</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2455889</t>
+          <t>2449392</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2611657</t>
+          <t>2600228</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>935564</t>
+          <t>935538</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1040713</t>
+          <t>1037481</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1222396</t>
+          <t>1216869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1334990</t>
+          <t>1328671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2188542</t>
+          <t>2190908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2337659</t>
+          <t>2335832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30686</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24417</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23316</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47254</t>
+          <t>47146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>34542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44959</t>
+          <t>44508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42228</t>
+          <t>41695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71660</t>
+          <t>72561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55283</t>
+          <t>56550</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86763</t>
+          <t>90307</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>58453</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92935</t>
+          <t>93977</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>120988</t>
+          <t>121649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168604</t>
+          <t>169308</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>824631</t>
+          <t>823512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>863671</t>
+          <t>863564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1153804</t>
+          <t>1154739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1196779</t>
+          <t>1197121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1990692</t>
+          <t>1992559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2052759</t>
+          <t>2050474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>32844</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58860</t>
+          <t>58128</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>22885</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>46780</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61023</t>
+          <t>61950</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>97350</t>
+          <t>97015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92779</t>
+          <t>91986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135734</t>
+          <t>133055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63024</t>
+          <t>64017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97693</t>
+          <t>97819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166915</t>
+          <t>163747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220766</t>
+          <t>219415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250536</t>
+          <t>252438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317360</t>
+          <t>315870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205747</t>
+          <t>206479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>264106</t>
+          <t>265475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>474223</t>
+          <t>474781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559488</t>
+          <t>565753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1417618</t>
+          <t>1422798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1498061</t>
+          <t>1495440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1308570</t>
+          <t>1308089</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1375254</t>
+          <t>1376670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2754865</t>
+          <t>2745066</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2853107</t>
+          <t>2848824</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>21516</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35175</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>52702</t>
+          <t>50842</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71624</t>
+          <t>69874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106874</t>
+          <t>104221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44835</t>
+          <t>46145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74875</t>
+          <t>78228</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123073</t>
+          <t>122774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167960</t>
+          <t>169719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>344078</t>
+          <t>345426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>380685</t>
+          <t>382922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>328850</t>
+          <t>327756</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>364516</t>
+          <t>363845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687336</t>
+          <t>686208</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737546</t>
+          <t>738954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52832</t>
+          <t>52635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84595</t>
+          <t>84664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42026</t>
+          <t>41593</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71463</t>
+          <t>72134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100282</t>
+          <t>99419</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145630</t>
+          <t>143599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126459</t>
+          <t>125852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114742</t>
+          <t>113406</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158484</t>
+          <t>160795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249724</t>
+          <t>251093</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>317670</t>
+          <t>316630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>402685</t>
+          <t>401916</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>482004</t>
+          <t>479096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>332704</t>
+          <t>330597</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>405912</t>
+          <t>405447</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>748803</t>
+          <t>752070</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>861095</t>
+          <t>863790</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2619676</t>
+          <t>2624218</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2714826</t>
+          <t>2712145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2823568</t>
+          <t>2824040</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2909191</t>
+          <t>2912930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5473769</t>
+          <t>5471730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5601290</t>
+          <t>5597028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>14365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32897</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>29985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55136</t>
+          <t>55742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29455</t>
+          <t>29521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>54609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61189</t>
+          <t>60554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94604</t>
+          <t>96637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75857</t>
+          <t>76788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112301</t>
+          <t>115342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57884</t>
+          <t>58734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92648</t>
+          <t>94193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>144222</t>
+          <t>146724</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>195583</t>
+          <t>195548</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>557159</t>
+          <t>556526</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>599938</t>
+          <t>601221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>800749</t>
+          <t>798724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>843133</t>
+          <t>844355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1366274</t>
+          <t>1368829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1428160</t>
+          <t>1433511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48263</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>38462</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67679</t>
+          <t>67442</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>96311</t>
+          <t>92931</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>136850</t>
+          <t>136753</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136914</t>
+          <t>135854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186468</t>
+          <t>186629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117208</t>
+          <t>120210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165766</t>
+          <t>166097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269592</t>
+          <t>263384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337000</t>
+          <t>334222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>378675</t>
+          <t>377731</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454232</t>
+          <t>456585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>352101</t>
+          <t>352221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>415822</t>
+          <t>421085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>748777</t>
+          <t>747955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>850060</t>
+          <t>849766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1356613</t>
+          <t>1355832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1443979</t>
+          <t>1442097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1332665</t>
+          <t>1332851</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1409870</t>
+          <t>1408551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2711147</t>
+          <t>2711480</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2828381</t>
+          <t>2829867</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35933</t>
+          <t>35061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>18263</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37419</t>
+          <t>39390</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36595</t>
+          <t>35426</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>65307</t>
+          <t>64981</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72965</t>
+          <t>72818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108212</t>
+          <t>108720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64924</t>
+          <t>61616</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98030</t>
+          <t>97435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145666</t>
+          <t>145625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194876</t>
+          <t>193287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>398378</t>
+          <t>399060</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>435635</t>
+          <t>438905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399427</t>
+          <t>398720</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>437932</t>
+          <t>438644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>811304</t>
+          <t>809979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>864990</t>
+          <t>865668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66902</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>104355</t>
+          <t>106192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66315</t>
+          <t>67901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104053</t>
+          <t>103923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>144011</t>
+          <t>144190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195132</t>
+          <t>195639</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195171</t>
+          <t>194768</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256315</t>
+          <t>253250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177058</t>
+          <t>176010</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231667</t>
+          <t>230480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388526</t>
+          <t>384151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468785</t>
+          <t>470675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>557632</t>
+          <t>551798</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>647098</t>
+          <t>647730</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,82 +7695,82 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>19,59%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>536367</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>496024</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>580003</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>15,6%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>16,87%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1136994</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>1072549</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>1201912</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>16,86%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>536367</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>494865</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>581893</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1136994</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1077662</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1204641</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2342015</t>
+          <t>2344404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2446655</t>
+          <t>2452872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2563357</t>
+          <t>2565984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2663717</t>
+          <t>2661066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4937191</t>
+          <t>4938965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5080031</t>
+          <t>5088432</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>34063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38523</t>
+          <t>39913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,22 +8397,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>24055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>42842</t>
+          <t>45249</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>32759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57198</t>
+          <t>57858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>59967</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42755</t>
+          <t>45059</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76727</t>
+          <t>78069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44794</t>
+          <t>47365</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>37430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58456</t>
+          <t>60868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>101789</t>
+          <t>107332</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82331</t>
+          <t>87539</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123857</t>
+          <t>130632</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>420329</t>
+          <t>476604</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>400602</t>
+          <t>455992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>438050</t>
+          <t>494966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>680076</t>
+          <t>741585</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>663949</t>
+          <t>726451</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>691804</t>
+          <t>754794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1100405</t>
+          <t>1218190</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1076146</t>
+          <t>1192288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1124852</t>
+          <t>1242407</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514208</t>
+          <t>577525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514208</t>
+          <t>577525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514208</t>
+          <t>577525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>749798</t>
+          <t>816027</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>749798</t>
+          <t>816027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749798</t>
+          <t>816027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1264006</t>
+          <t>1393553</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1264006</t>
+          <t>1393553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1264006</t>
+          <t>1393553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>36275</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>33394</t>
+          <t>41834</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21549</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46869</t>
+          <t>59448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>123380</t>
+          <t>128428</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85389</t>
+          <t>103221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157387</t>
+          <t>157810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>98668</t>
+          <t>103166</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72990</t>
+          <t>84657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121406</t>
+          <t>120276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>222048</t>
+          <t>231594</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175515</t>
+          <t>200020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>265091</t>
+          <t>261270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>272057</t>
+          <t>284114</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>186610</t>
+          <t>246730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327946</t>
+          <t>323060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>225160</t>
+          <t>243934</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164178</t>
+          <t>219941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263710</t>
+          <t>274285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>497217</t>
+          <t>528048</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>399596</t>
+          <t>483710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>569483</t>
+          <t>579660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1873190</t>
+          <t>1791313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1799988</t>
+          <t>1745377</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1997913</t>
+          <t>1835266</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1887002</t>
+          <t>1789119</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1832404</t>
+          <t>1755242</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1975875</t>
+          <t>1818154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3760193</t>
+          <t>3580432</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3667177</t>
+          <t>3527097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3919479</t>
+          <t>3636387</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2283092</t>
+          <t>2222672</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2283092</t>
+          <t>2222672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2283092</t>
+          <t>2222672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2229759</t>
+          <t>2159235</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2229759</t>
+          <t>2159235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2229759</t>
+          <t>2159235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4512852</t>
+          <t>4381908</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4512852</t>
+          <t>4381908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4512852</t>
+          <t>4381908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24637</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16263</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38708</t>
+          <t>40024</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>21462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>44736</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>63055</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>62361</t>
+          <t>68350</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>52378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81906</t>
+          <t>87951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61779</t>
+          <t>66581</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50960</t>
+          <t>53348</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76476</t>
+          <t>82733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>124139</t>
+          <t>134930</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105728</t>
+          <t>116456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146950</t>
+          <t>158801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>547901</t>
+          <t>613723</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>528188</t>
+          <t>590737</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>566810</t>
+          <t>632437</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>571889</t>
+          <t>639108</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554903</t>
+          <t>620408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>585163</t>
+          <t>654558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1119790</t>
+          <t>1252831</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1095376</t>
+          <t>1226937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1143534</t>
+          <t>1277238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,61%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>657584</t>
+          <t>731036</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>657584</t>
+          <t>731036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>657584</t>
+          <t>731036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1295246</t>
+          <t>1441441</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1295246</t>
+          <t>1441441</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1295246</t>
+          <t>1441441</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>34906</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>24963</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39870</t>
+          <t>52750</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>36426</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>26392</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45711</t>
+          <t>51169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>58944</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77357</t>
+          <t>93257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>174361</t>
+          <t>181626</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129946</t>
+          <t>156504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206920</t>
+          <t>217480</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>135265</t>
+          <t>142180</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109573</t>
+          <t>125123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158878</t>
+          <t>167800</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>309626</t>
+          <t>323806</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>264314</t>
+          <t>286333</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352995</t>
+          <t>364074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>391413</t>
+          <t>412430</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>298904</t>
+          <t>373152</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>447137</t>
+          <t>460675</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>331733</t>
+          <t>357880</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>270899</t>
+          <t>324899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>371236</t>
+          <t>389385</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>723146</t>
+          <t>770310</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>619575</t>
+          <t>714554</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>797306</t>
+          <t>823559</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2841419</t>
+          <t>2881640</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2769408</t>
+          <t>2824821</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2976681</t>
+          <t>2928553</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3138968</t>
+          <t>3169813</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3084967</t>
+          <t>3130880</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3221088</t>
+          <t>3210071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5980387</t>
+          <t>6051452</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5887289</t>
+          <t>5985044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6129354</t>
+          <t>6119184</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>84,79%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3434962</t>
+          <t>3510602</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3434962</t>
+          <t>3510602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3434962</t>
+          <t>3510602</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3637141</t>
+          <t>3706299</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3637141</t>
+          <t>3706299</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3637141</t>
+          <t>3706299</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7072103</t>
+          <t>7216901</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7072103</t>
+          <t>7216901</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7072103</t>
+          <t>7216901</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
